--- a/macro/양식/상위키워드조회_양식.xlsx
+++ b/macro/양식/상위키워드조회_양식.xlsx
@@ -459,7 +459,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -470,7 +470,7 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>키워드</t>
+          <t>키워드 (콤마로 구분, 최대 100개)</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>강남 맛집</t>
+          <t>강남 맛집,강남 카페,강남 헤어숍</t>
         </is>
       </c>
     </row>
